--- a/data/incremental/incremental_08_curico_manual.xlsx
+++ b/data/incremental/incremental_08_curico_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="42" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Brasas+Curic%C3%B3/@-34.9867054,-71.2130128,17z/data=!3m1!4b1!4m6!3m5!1s0x9664570112b48ed1:0xa16e8c9d8e070ab6!8m2!3d-34.9867054!4d-71.2130128!16s%2Fg%2F11s0w28p80?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Brasas+Curic%C3%B3/data=!4m7!3m6!1s0x9664570112b48ed1:0xa16e8c9d8e070ab6!8m2!3d-34.9867054!4d-71.2130128!16s%2Fg%2F11s0w28p80!19sChIJ0Y60EgFXZJYRtgoHjp2MbqE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Fuego+Bendito/@-34.9863974,-71.2301915,17z/data=!3m1!4b1!4m6!3m5!1s0x966457afd9136567:0xc43479034c42c4be!8m2!3d-34.9863974!4d-71.2301915!16s%2Fg%2F11c1xj9rk_?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Fuego+Bendito/data=!4m7!3m6!1s0x966457afd9136567:0xc43479034c42c4be!8m2!3d-34.9863974!4d-71.2301915!16s%2Fg%2F11c1xj9rk_!19sChIJZ2UT2a9XZJYRvsRCTAN5NMQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>593</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,34 +938,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trattoria La Pasta</t>
+          <t>Restaurante Fuente Curicana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Carrera 121, 3341737 Curicó, Maule</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>9 9093 9820</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://cartas.horecaqr.com/c/trattorialapasta</t>
-        </is>
-      </c>
+          <t>Longitudinal sur km 191, 3340000 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -973,17 +965,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Trattoria+La+Pasta/@-34.9851392,-71.231846,17z/data=!3m1!4b1!4m6!3m5!1s0x966457d4b38ed84f:0x20a5ccbbc8917921!8m2!3d-34.9851392!4d-71.231846!16s%2Fg%2F11h41w0vc3?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+Fuente+Curicana/data=!4m7!3m6!1s0x9664f956f788b27b:0xbc81ea1f8e364bd2!8m2!3d-34.9884756!4d-71.2225595!16s%2Fg%2F11k58cxts2!19sChIJe7KI91b5ZJYR0ks2jh_qgbw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-34.9851392</t>
+          <t>-34.9884756</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-71.231846</t>
+          <t>-71.2225595</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1008,12 +1000,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1036,31 +1028,43 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Restaurante Fuente Curicana</t>
+          <t>Trattoria La Pasta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>298</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Longitudinal sur km 191, 3340000 Curicó, Maule</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>Carrera 121, 3341737 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9 9093 9820</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://cartas.horecaqr.com/c/trattorialapasta</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1068,17 +1072,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Fuente+Curicana/data=!4m7!3m6!1s0x9664f956f788b27b:0xbc81ea1f8e364bd2!8m2!3d-34.9884756!4d-71.2225595!16s%2Fg%2F11k58cxts2!19sChIJe7KI91b5ZJYR0ks2jh_qgbw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Trattoria+La+Pasta/data=!4m7!3m6!1s0x966457d4b38ed84f:0x20a5ccbbc8917921!8m2!3d-34.9851392!4d-71.231846!16s%2Fg%2F11h41w0vc3!19sChIJT9iOs9RXZJYRIXmRyLvMpSA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-34.9884756</t>
+          <t>-34.9851392</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-71.2225595</t>
+          <t>-71.231846</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1103,12 +1107,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1131,11 +1135,7 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Milenario+Restaurante/@-34.9846867,-71.2367248,17z/data=!3m1!4b1!4m6!3m5!1s0x96645783fd458cbb:0x44f6dfab4b45c6d5!8m2!3d-34.9846867!4d-71.2367248!16s%2Fg%2F11vr1d1ll3?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Milenario+Restaurante/data=!4m7!3m6!1s0x96645783fd458cbb:0x44f6dfab4b45c6d5!8m2!3d-34.9846867!4d-71.2367248!16s%2Fg%2F11vr1d1ll3!19sChIJu4xF_YNXZJYR1cZFS6vf9kQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Rinc%C3%B3n+Marino/@-34.9930934,-71.2391405,17z/data=!3m1!4b1!4m6!3m5!1s0x966457aa6d97bb05:0x5f6ed0c99dab5cc5!8m2!3d-34.9930934!4d-71.2391405!16s%2Fg%2F11fxvxg_yt?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rinc%C3%B3n+Marino/data=!4m7!3m6!1s0x966457aa6d97bb05:0x5f6ed0c99dab5cc5!8m2!3d-34.9930934!4d-71.2391405!16s%2Fg%2F11fxvxg_yt!19sChIJBbuXbapXZJYRxVyrncnQbl8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1540,52 +1540,48 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Restaurant Mi Perú Curicó</t>
+          <t>Restaurant Zhong yi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>627</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yungay 767 Curicó, 3340000 Maule, Curicó, Maule</t>
+          <t>Av. Camilo Henríquez 380, 3341582 Curicó, Maule</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(75) 234 2987</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>http://www.miperu.cl/</t>
-        </is>
-      </c>
+          <t>(75) 232 8168</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Mi+Per%C3%BA+Curic%C3%B3/@-34.9829755,-71.2404993,17z/data=!3m1!4b1!4m6!3m5!1s0x966457e056870285:0x37b9a0af8159ac3a!8m2!3d-34.9829755!4d-71.2404993!16s%2Fg%2F11h4lcbpfb?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Zhong+yi/data=!4m7!3m6!1s0x96645709f83c55c9:0x5ee599a7c239913d!8m2!3d-34.98144!4d-71.2403999!16s%2Fg%2F11c60jqq9t!19sChIJyVU8-AlXZJYRPZE5wqeZ5V4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-34.9829755</t>
+          <t>-34.98144</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-71.2404993</t>
+          <t>-71.2403999</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1610,12 +1606,12 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1643,52 +1639,52 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HIKI STREET FOOD</t>
+          <t>Lanzas y Fuego</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>102</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Argomedo 535, 3341862 Curicó, Maule</t>
+          <t>Carrera 171, 3341737 Curicó, Maule</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9 7147 7257</t>
+          <t>(75) 276 2665</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hiki_street_food/</t>
+          <t>http://www.lanzasyfuego.cl/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante especializado en barbacoa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HIKI+STREET+FOOD/data=!4m7!3m6!1s0x9664575bf19b8bf9:0x87934df94f146b1d!8m2!3d-34.987194!4d-71.2418365!16s%2Fg%2F11s1rtmpl9!19sChIJ-Yub8VtXZJYRHWsUT_lNk4c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Lanzas+y+Fuego/data=!4m7!3m6!1s0x96645797d6a3d403:0x261665aea47f2fe0!8m2!3d-34.9851614!4d-71.2311832!16s%2Fg%2F11kb4rl__6!19sChIJA9Sj1pdXZJYR4C9_pK5lFiY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-34.987194</t>
+          <t>-34.9851614</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-71.2418365</t>
+          <t>-71.2311832</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1713,7 +1709,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1746,52 +1742,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lanzas y Fuego</t>
+          <t>Mi Casa Restaurante</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>536</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carrera 171, 3341737 Curicó, Maule</t>
+          <t>Peña 871, 3341566 Curicó, Maule</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(75) 276 2665</t>
+          <t>(75) 274 7095</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>http://www.lanzasyfuego.cl/</t>
+          <t>https://www.facebook.com/Mi-Casa-Restaurante-167038006818879/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Restaurante especializado en barbacoa</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lanzas+y+Fuego/data=!4m7!3m6!1s0x96645797d6a3d403:0x261665aea47f2fe0!8m2!3d-34.9851614!4d-71.2311832!16s%2Fg%2F11kb4rl__6!19sChIJA9Sj1pdXZJYR4C9_pK5lFiY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Mi+Casa+Restaurante/data=!4m7!3m6!1s0x9664570989291387:0xae7191c028006b89!8m2!3d-34.9819444!4d-71.2419444!16s%2Fg%2F11f08930gz!19sChIJhxMpiQlXZJYRiWsAKMCRca4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-34.9851614</t>
+          <t>-34.9819444</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-71.2311832</t>
+          <t>-71.2419444</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1816,7 +1812,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1849,7 +1845,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Restaurant Zhong yi</t>
+          <t>Andö</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1859,17 +1855,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Av. Camilo Henríquez 380, 3341582 Curicó, Maule</t>
+          <t>Av. España 109, 3340000 Curicó, Maule</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(75) 232 8168</t>
+          <t>(75) 226 0804</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1880,17 +1876,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Zhong+yi/data=!4m7!3m6!1s0x96645709f83c55c9:0x5ee599a7c239913d!8m2!3d-34.98144!4d-71.2403999!16s%2Fg%2F11c60jqq9t!19sChIJyVU8-AlXZJYRPZE5wqeZ5V4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/And%C3%B6/data=!4m7!3m6!1s0x966457af5186b1c3:0xf2d4ea5007c3a253!8m2!3d-34.9861433!4d-71.2290125!16s%2Fg%2F11dxdhgzk4!19sChIJw7GGUa9XZJYRU6LDB1Dq1PI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-34.98144</t>
+          <t>-34.9861433</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-71.2403999</t>
+          <t>-71.2290125</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1915,7 +1911,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1948,48 +1944,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andö</t>
+          <t>Restaurant Mi Perú Curicó</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>486</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Av. España 109, 3340000 Curicó, Maule</t>
+          <t>yungay 767 Curicó, 3340000 Maule, Curicó, Maule</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(75) 226 0804</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>(75) 234 2987</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>http://www.miperu.cl/</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/And%C3%B6/@-34.9861433,-71.2290125,17z/data=!3m1!4b1!4m6!3m5!1s0x966457af5186b1c3:0xf2d4ea5007c3a253!8m2!3d-34.9861433!4d-71.2290125!16s%2Fg%2F11dxdhgzk4?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Mi+Per%C3%BA+Curic%C3%B3/data=!4m7!3m6!1s0x966457e056870285:0x37b9a0af8159ac3a!8m2!3d-34.9829755!4d-71.2404993!16s%2Fg%2F11h4lcbpfb!19sChIJhQKHVuBXZJYROqxZga-guTc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-34.9861433</t>
+          <t>-34.9829755</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-71.2290125</t>
+          <t>-71.2404993</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2047,52 +2047,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Restaurante Oveja huasa</t>
+          <t>Restaurant Polinesia</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Los Olivos 226, 3340000 Curicó, Maule</t>
+          <t>Cam. A Licantén 1455, 3340000 Curicó, Maule</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9 6553 7030</t>
+          <t>9 7527 5435</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>http://www.ovejahuasa.cl/</t>
+          <t>https://www.instagram.com/restaurant_polinesia/?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Oveja+huasa/data=!4m7!3m6!1s0x966457e1225f383f:0x361e5e6dd7901317!8m2!3d-34.9741027!4d-71.2177091!16s%2Fg%2F11v3sv_834!19sChIJPzhfIuFXZJYRFxOQ121eHjY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurant+Polinesia/data=!4m7!3m6!1s0x966457711abd2c91:0x32c8d699eabb9281!8m2!3d-34.9770753!4d-71.2550231!16s%2Fg%2F11tdlbm90_!19sChIJkSy9GnFXZJYRgZK76pnWyDI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-34.9741027</t>
+          <t>-34.9770753</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-71.2177091</t>
+          <t>-71.2550231</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Inti+Pehuen+Curico/@-34.9869479,-71.2136668,17z/data=!3m1!4b1!4m6!3m5!1s0x966457000f16e50d:0x658865810c1db26e!8m2!3d-34.9869479!4d-71.2136668!16s%2Fg%2F11vk4l61n8?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+Inti+Pehuen+Curico/data=!4m7!3m6!1s0x966457000f16e50d:0x658865810c1db26e!8m2!3d-34.9869479!4d-71.2136668!16s%2Fg%2F11vk4l61n8!19sChIJDeUWDwBXZJYRbrIdDIFliGU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2360,32 +2360,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Restaurant Polinesia</t>
+          <t>HIKI STREET FOOD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cam. A Licantén 1455, 3340000 Curicó, Maule</t>
+          <t>Argomedo 535, 3341862 Curicó, Maule</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9 7527 5435</t>
+          <t>9 7147 7257</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/restaurant_polinesia/?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/hiki_street_food/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Polinesia/data=!4m7!3m6!1s0x966457711abd2c91:0x32c8d699eabb9281!8m2!3d-34.9770753!4d-71.2550231!16s%2Fg%2F11tdlbm90_!19sChIJkSy9GnFXZJYRgZK76pnWyDI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/HIKI+STREET+FOOD/data=!4m7!3m6!1s0x9664575bf19b8bf9:0x87934df94f146b1d!8m2!3d-34.987194!4d-71.2418365!16s%2Fg%2F11s1rtmpl9!19sChIJ-Yub8VtXZJYRHWsUT_lNk4c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-34.9770753</t>
+          <t>-34.987194</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-71.2550231</t>
+          <t>-71.2418365</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2463,48 +2463,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Restaurante Pasion Limeña</t>
+          <t>Restaurante Oveja huasa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Villota 639, 8320000 Curicó, Maule</t>
+          <t>Los Olivos 226, 3340000 Curicó, Maule</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(75) 274 7311</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>9 6553 7030</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>http://www.ovejahuasa.cl/</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante chileno</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Pasion+Lime%C3%B1a/data=!4m7!3m6!1s0x96645716d1584e13:0xe23d5c70d69aec44!8m2!3d-34.9884289!4d-71.2430858!16s%2Fg%2F11j3wh0bb1!19sChIJE05Y0RZXZJYRROya1nBcPeI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Oveja+huasa/data=!4m7!3m6!1s0x966457e1225f383f:0x361e5e6dd7901317!8m2!3d-34.9741027!4d-71.2177091!16s%2Fg%2F11v3sv_834!19sChIJPzhfIuFXZJYRFxOQ121eHjY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-34.9884289</t>
+          <t>-34.9741027</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-71.2430858</t>
+          <t>-71.2177091</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2529,12 +2533,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2562,52 +2566,48 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mi Casa Restaurante</t>
+          <t>Restaurante Pasion Limeña</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>329</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Peña 871, 3341566 Curicó, Maule</t>
+          <t>Villota 639, 8320000 Curicó, Maule</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(75) 274 7095</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Mi-Casa-Restaurante-167038006818879/</t>
-        </is>
-      </c>
+          <t>(75) 274 7311</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante chileno</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mi+Casa+Restaurante/@-34.9819444,-71.2419444,17z/data=!3m1!4b1!4m6!3m5!1s0x9664570989291387:0xae7191c028006b89!8m2!3d-34.9819444!4d-71.2419444!16s%2Fg%2F11f08930gz?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+Pasion+Lime%C3%B1a/data=!4m7!3m6!1s0x96645716d1584e13:0xe23d5c70d69aec44!8m2!3d-34.9884289!4d-71.2430858!16s%2Fg%2F11j3wh0bb1!19sChIJE05Y0RZXZJYRROya1nBcPeI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-34.9819444</t>
+          <t>-34.9884289</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-71.2419444</t>
+          <t>-71.2430858</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2665,48 +2665,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Restaurant Chino El León Dorado</t>
+          <t>Restaurante Peruvian</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Carrera 7, 3341735 Curicó, Maule</t>
+          <t>Av. Amsterdam 1664, 3345659 Curicó, Maule</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9 8494 8366</t>
+          <t>9 6403 5028</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Chino+El+Le%C3%B3n+Dorado/data=!4m7!3m6!1s0x966457a5f8854d1d:0x812b648301ea7c41!8m2!3d-34.9853675!4d-71.2334501!16s%2Fg%2F11tsjyt70j!19sChIJHU2F-KVXZJYRQXzqAYNkK4E?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Peruvian/data=!4m7!3m6!1s0x966457235ce103cf:0x4d0344c3e7ea5eb!8m2!3d-34.9621278!4d-71.2022538!16s%2Fg%2F11nxcdmm76!19sChIJzwPhXCNXZJYR66V-Pkw00AQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-34.9853675</t>
+          <t>-34.9621278</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-71.2334501</t>
+          <t>-71.2022538</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2764,34 +2764,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fuente de Soda " El Panzón "</t>
+          <t>Ají criollo de Curico</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Av. Freire 184, 3340000 Curicó, Maule</t>
+          <t>isabel la catolica 392 Curicó, 3343807 Maule, Curicó, Maule</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(75) 274 6048</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>http://www.panzoncurico.cl/</t>
-        </is>
-      </c>
+          <t>9 7121 5452</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2799,17 +2795,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Fuente+de+Soda+%22+El+Panz%C3%B3n+%22/data=!4m7!3m6!1s0x966457a1b18ffbc9:0xf8dbe549713d259d!8m2!3d-34.9770172!4d-71.2378876!16s%2Fg%2F119tsr0mn!19sChIJyfuPsaFXZJYRnSU9cUnl2_g?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Aj%C3%AD+criollo+de+Curico/data=!4m7!3m6!1s0x966457e42b683f4b:0x9056921874731942!8m2!3d-34.9852575!4d-71.2245606!16s%2Fg%2F11rr5j3jf7!19sChIJSz9oK-RXZJYRQhlzdBiSVpA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-34.9770172</t>
+          <t>-34.9852575</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-71.2378876</t>
+          <t>-71.2245606</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2834,12 +2830,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2867,52 +2863,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NOVU</t>
+          <t>ComoRoble Restaurant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>569</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Carrera 301, 3340000 Curicó, Maule</t>
+          <t>Longitudinal Sur, Curicó, Romeral, Maule</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9 9671 7253</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>http://www.novu.cl/</t>
-        </is>
-      </c>
+          <t>9 9449 1072</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pub restaurante</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/NOVU/@-34.984909,-71.2295317,17z/data=!3m1!4b1!4m6!3m5!1s0x966457570a4a381b:0xe2725e2bdd47b27e!8m2!3d-34.984909!4d-71.2295317!16s%2Fg%2F11s4w6gg0n?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/ComoRoble+Restaurant/data=!4m7!3m6!1s0x9664f809c6e11b3d:0x887c8c479ee63490!8m2!3d-34.960998!4d-71.1910314!16s%2Fg%2F11f57s2shf!19sChIJPRvhxgn4ZJYRkDTmnkeMfIg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-34.984909</t>
+          <t>-34.960998</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-71.2295317</t>
+          <t>-71.1910314</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2937,12 +2929,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2970,48 +2962,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Restaurant Perla Azul</t>
+          <t>La Vizcaya Curicó</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Av. España 109, 3340001 Curicó, Maule</t>
+          <t>Av. España 215, Local 4, 3340000 Curicó, Maule</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(75) 222 0888</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>9 2724 5151</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lavizcaya.curico</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Restaurante chino</t>
+          <t>Restaurante de cocina española</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Perla+Azul/data=!4m7!3m6!1s0x966457afc033d69f:0xa5ffbc7e0cea6f23!8m2!3d-34.986116!4d-71.229345!16s%2Fg%2F11b7q60d8q!19sChIJn9YzwK9XZJYRI2_qDH68_6U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Vizcaya+Curic%C3%B3/data=!4m7!3m6!1s0x9664576c93ab7fc7:0xd439b67218823c36!8m2!3d-34.9861526!4d-71.2283424!16s%2Fg%2F11xkwk5ydv!19sChIJx3-rk2xXZJYRNjyCGHK2OdQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-34.986116</t>
+          <t>-34.9861526</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-71.229345</t>
+          <t>-71.2283424</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3036,12 +3032,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3069,7 +3065,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marivá Restaurant</t>
+          <t>Lungo Restaurante y Cafetería</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3079,38 +3075,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>154</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Av. España 692, 3341853 Curicó, Maule</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Av. España 734, 3340000 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>9 7545 3633</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://toteat.shop/r/cl/Mariva/22804/checkin/menu</t>
+          <t>http://lungo.cl/carta-restaurante</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Cafetería</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mariv%C3%A1+Restaurant/data=!4m7!3m6!1s0x9664570043d01c99:0x772b77f7070e01ab!8m2!3d-34.9857874!4d-71.2263104!16s%2Fg%2F11nbnj4x3c!19sChIJmRzQQwBXZJYRqwEOB_d3K3c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Lungo+Restaurante+y+Cafeter%C3%ADa/data=!4m7!3m6!1s0x966457115e8eb7f7:0xde6ecfb1c763127c!8m2!3d-34.9854289!4d-71.2250875!16s%2Fg%2F11y1rvfcl4!19sChIJ97eOXhFXZJYRfBJjx7HPbt4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-34.9857874</t>
+          <t>-34.9854289</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-71.2263104</t>
+          <t>-71.2250875</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3135,17 +3135,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R26" t="inlineStr"/>
@@ -3165,12 +3165,515 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
+          <t>Revisar: parece cafeteria; Revisar: parece cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brasas Mall Curicó</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Av. O´Higgins 287, Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Restaurante familiar</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Brasas+Mall+Curic%C3%B3/data=!4m7!3m6!1s0x9664570028e0b217:0x57c616f40cd9e524!8m2!3d-34.9908641!4d-71.2441545!16s%2Fg%2F11y6k6_2fl!19sChIJF7LgKABXZJYRJOXZDPQWxlc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-34.9908641</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-71.2441545</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estadio Español de Curico</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Av. España 802, 3340000 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(75) 231 0383</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>http://estadioespanolcurico.cl/web/</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Estadio+Espa%C3%B1ol+de+Curico/data=!4m7!3m6!1s0x966457b0b172e3e3:0x8571f3c83e9634be!8m2!3d-34.9853057!4d-71.2229919!16s%2Fg%2F1td8_b42!19sChIJ4-NysbBXZJYRvjSWPsjzcYU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-34.9853057</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-71.2229919</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Club Italiano</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Estado 531, 3341796 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(75) 231 0482</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Club+Italiano/data=!4m7!3m6!1s0x966457081121c371:0xfd60816305af93f0!8m2!3d-34.9860617!4d-71.2418227!16s%2Fg%2F11h9y66mm0!19sChIJccMhEQhXZJYR8JOvBWOBYP0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-34.9860617</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-71.2418227</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Restaurant Chino El León Dorado</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carrera 7, 3341735 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9 8494 8366</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurant+Chino+El+Le%C3%B3n+Dorado/data=!4m7!3m6!1s0x966457a5f8854d1d:0x812b648301ea7c41!8m2!3d-34.9853675!4d-71.2334501!16s%2Fg%2F11tsjyt70j!19sChIJHU2F-KVXZJYRQXzqAYNkK4E?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-34.9853675</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-71.2334501</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Marivá Restaurant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av. España 692, 3341853 Curicó, Maule</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://toteat.shop/r/cl/Mariva/22804/checkin/menu</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Mariv%C3%A1+Restaurant/data=!4m7!3m6!1s0x9664570043d01c99:0x772b77f7070e01ab!8m2!3d-34.9857874!4d-71.2263104!16s%2Fg%2F11nbnj4x3c!19sChIJmRzQQwBXZJYRqwEOB_d3K3c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-34.9857874</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-71.2263104</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr">
+        <is>
           <t>Sin teléfono visible</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG26"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>